--- a/pandemic-loss-modeling/exceedance_results/bernstein_1600.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/bernstein_1600.xlsx
@@ -393,7 +393,7 @@
         <v>0.001</v>
       </c>
       <c r="B2">
-        <v>0.9599900153990543</v>
+        <v>0.890268892028197</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>0.002</v>
       </c>
       <c r="B3">
-        <v>0.9230400330954205</v>
+        <v>0.802195185960294</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>7.2</v>
       </c>
       <c r="B4">
-        <v>0.00312329197276536</v>
+        <v>0.001093934894911173</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>28</v>
       </c>
       <c r="B5">
-        <v>0.0007909408080863116</v>
+        <v>0.0002796394860172561</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>45</v>
       </c>
       <c r="B6">
-        <v>0.00048924703094509</v>
+        <v>0.0001736068601425977</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -433,7 +433,7 @@
         <v>86</v>
       </c>
       <c r="B7">
-        <v>0.0002538997096630055</v>
+        <v>9.055641475553972E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -441,7 +441,7 @@
         <v>150</v>
       </c>
       <c r="B8">
-        <v>0.0001445274328776631</v>
+        <v>5.177762395711147E-05</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -449,7 +449,7 @@
         <v>200</v>
       </c>
       <c r="B9">
-        <v>0.0001079913333998318</v>
+        <v>3.877820723644303E-05</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -457,7 +457,7 @@
         <v>220</v>
       </c>
       <c r="B10">
-        <v>9.805225465561176E-05</v>
+        <v>3.52363346789119E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -465,7 +465,7 @@
         <v>250</v>
       </c>
       <c r="B11">
-        <v>8.61424332684273E-05</v>
+        <v>3.098839865952652E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -473,7 +473,7 @@
         <v>280</v>
       </c>
       <c r="B12">
-        <v>7.679933369250712E-05</v>
+        <v>2.7652714609963E-05</v>
       </c>
     </row>
   </sheetData>

--- a/pandemic-loss-modeling/exceedance_results/bernstein_1600.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/bernstein_1600.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -390,89 +390,81 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.890268892028197</v>
+        <v>0.4474311872472255</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>0.002</v>
+        <v>7.2</v>
       </c>
       <c r="B3">
-        <v>0.802195185960294</v>
+        <v>0.001093934894911173</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>0.001093934894911173</v>
+        <v>0.0002796394860172561</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="B5">
-        <v>0.0002796394860172561</v>
+        <v>0.0001736068601425977</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="B6">
-        <v>0.0001736068601425977</v>
+        <v>9.055641475553972E-05</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="B7">
-        <v>9.055641475553972E-05</v>
+        <v>5.177762395711147E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="B8">
-        <v>5.177762395711147E-05</v>
+        <v>3.877820723644303E-05</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B9">
-        <v>3.877820723644303E-05</v>
+        <v>3.52363346789119E-05</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="B10">
-        <v>3.52363346789119E-05</v>
+        <v>3.098839865952652E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="B11">
-        <v>3.098839865952652E-05</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>280</v>
-      </c>
-      <c r="B12">
         <v>2.7652714609963E-05</v>
       </c>
     </row>

--- a/pandemic-loss-modeling/exceedance_results/bernstein_1600.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/bernstein_1600.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -398,73 +398,249 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>7.2</v>
+        <v>0.04</v>
       </c>
       <c r="B3">
-        <v>0.001093934894911173</v>
+        <v>0.1678755826729061</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>28</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="B4">
-        <v>0.0002796394860172561</v>
+        <v>0.1031879735094328</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>45</v>
+        <v>0.08</v>
       </c>
       <c r="B5">
-        <v>0.0001736068601425977</v>
+        <v>0.09142802691681944</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>86</v>
+        <v>0.1</v>
       </c>
       <c r="B6">
-        <v>9.055641475553972E-05</v>
+        <v>0.07444555437794789</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>150</v>
+        <v>0.4</v>
       </c>
       <c r="B7">
-        <v>5.177762395711147E-05</v>
+        <v>0.01959717617828875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>200</v>
+        <v>0.7</v>
       </c>
       <c r="B8">
-        <v>3.877820723644303E-05</v>
+        <v>0.01126419487927777</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="B9">
-        <v>3.52363346789119E-05</v>
+        <v>0.007898382589325677</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="B10">
-        <v>3.098839865952652E-05</v>
+        <v>0.001973054570945013</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>0.001125311327832581</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>0.0009841373700238795</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>0.0007865973553566821</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>0.0005234843747126366</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>20</v>
+      </c>
+      <c r="B15">
+        <v>0.0003921052894529612</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>28</v>
+      </c>
+      <c r="B16">
+        <v>0.0002796394860172561</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>40</v>
+      </c>
+      <c r="B17">
+        <v>0.0001954177501551968</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>45</v>
+      </c>
+      <c r="B18">
+        <v>0.0001736068601425977</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>70</v>
+      </c>
+      <c r="B19">
+        <v>0.0001113665970152572</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>86</v>
+      </c>
+      <c r="B20">
+        <v>9.055641475553972E-05</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>100</v>
+      </c>
+      <c r="B21">
+        <v>7.782113976192839E-05</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>120</v>
+      </c>
+      <c r="B22">
+        <v>6.479303702114543E-05</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>150</v>
+      </c>
+      <c r="B23">
+        <v>5.177762395711147E-05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>170</v>
+      </c>
+      <c r="B24">
+        <v>4.565799228504844E-05</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>190</v>
+      </c>
+      <c r="B25">
+        <v>4.082949544056699E-05</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>200</v>
+      </c>
+      <c r="B26">
+        <v>3.877820723644303E-05</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>220</v>
+      </c>
+      <c r="B27">
+        <v>3.52363346789119E-05</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>230</v>
+      </c>
+      <c r="B28">
+        <v>3.369692172114733E-05</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>240</v>
+      </c>
+      <c r="B29">
+        <v>3.228609430417705E-05</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>250</v>
+      </c>
+      <c r="B30">
+        <v>3.098839865952652E-05</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>260</v>
+      </c>
+      <c r="B31">
+        <v>2.97907611683391E-05</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>270</v>
+      </c>
+      <c r="B32">
+        <v>2.868204720998861E-05</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
         <v>280</v>
       </c>
-      <c r="B11">
+      <c r="B33">
         <v>2.7652714609963E-05</v>
       </c>
     </row>
